--- a/seed-data/strongman_exercise_database.xlsx
+++ b/seed-data/strongman_exercise_database.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="314">
   <si>
     <t xml:space="preserve">Exercise ID</t>
   </si>
@@ -951,6 +951,20 @@
   </si>
   <si>
     <t xml:space="preserve">Any specific weights/loads mentioned in Description / Cues are illustrative training ranges from general strongman-training knowledge, not figures verified against a named source or official competition standard — treat them as placeholders when seeding real content.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes/y/1/true (case-insensitive) turns on embedded playback for this row's Video Reference, if it's a YouTube link to one specific video (not a search-results link, which has no single video to embed) - leave blank (or anything else) for no. Turning this on is your confirmation that you have the right to embed that specific video. If you share this exercise library with embedding turned on, you're responsible for that - the app doesn't review library content, it only provides the platform. See the app's Disclaimer (Settings &gt; About) for the full policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using AI to convert your own exercise list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you already have a list of exercises written down somewhere (a document, notes app, an old spreadsheet, or a coach's program), you can ask an AI assistant to fill in this template for you instead of doing it by hand. Attach this file to your AI assistant of choice and adapt this prompt:
+"I'm attaching a spreadsheet template for a workout-tracking app's exercise library. Fill in the 'Exercises' tab using the exercise list I describe below, following the 'Legend' tab's column definitions exactly - Difficulty must be exactly one of Beginner/Intermediate/Advanced. Leave the 'Embedding' column blank unless I specifically tell you a video should be embedded, and never invent a video link yourself. Don't guess or invent values for any column I haven't given you information for - leave those cells blank instead. Return the completed spreadsheet in the same column order as the template.
+[describe your exercises here, or paste your existing list]"</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1411,6 +1425,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1446,6 +1461,9 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2812,7 +2830,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -2933,11 +2951,33 @@
       </c>
       <c r="B17" s="11"/>
     </row>
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/seed-data/strongman_exercise_database.xlsx
+++ b/seed-data/strongman_exercise_database.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="370">
   <si>
     <t xml:space="preserve">Exercise ID</t>
   </si>
@@ -965,6 +965,174 @@
     <t xml:space="preserve">If you already have a list of exercises written down somewhere (a document, notes app, an old spreadsheet, or a coach's program), you can ask an AI assistant to fill in this template for you instead of doing it by hand. Attach this file to your AI assistant of choice and adapt this prompt:
 "I'm attaching a spreadsheet template for a workout-tracking app's exercise library. Fill in the 'Exercises' tab using the exercise list I describe below, following the 'Legend' tab's column definitions exactly - Difficulty must be exactly one of Beginner/Intermediate/Advanced. Leave the 'Embedding' column blank unless I specifically tell you a video should be embedded, and never invent a video link yourself. Don't guess or invent values for any column I haven't given you information for - leave those cells blank instead. Return the completed spreadsheet in the same column order as the template.
 [describe your exercises here, or paste your existing list]"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable Row (Seated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squeeze the shoulder blades together at the finish; keep a slight lean back throughout, not a big rock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoid rounding the lower back to add range at the finish - stop the pull where your torso naturally stops moving.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Cable+Row+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable Tricep Pushdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep elbows pinned to your sides throughout; let the triceps do the work rather than leaning on the bar with body weight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't let the elbows drift forward as the weight gets heavy - that shifts load onto the shoulders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Tricep+Pushdown+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Press Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A safer entry point than a free-bar squat for building leg strength - feet shoulder-width on the platform; lower until knees reach roughly 90 degrees.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never let the lower back round off the pad at the bottom of the rep; don't lock the knees out hard at the top.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Press+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lat Pulldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lat Pulldown Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull the bar to the upper chest, driving the elbows down and back rather than pulling with the arms alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoid leaning back excessively or using momentum to move the weight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Lat+Pulldown+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Machine Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The fixed bar path makes this a good option for practicing squat depth and tempo without needing a spotter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position feet slightly forward of the bar, not directly under it, to keep the movement path comfortable for the knees.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Squat+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Extension Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An isolation move for the quads; extend the knees fully then lower under control rather than dropping the weight stack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoid using momentum by swinging into the first few reps - start each set under control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Extension+Machine+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seated Leg Curl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Curl Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An isolation move for the hamstrings; curl through a full range and pause briefly at full contraction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep the hips pressed into the seat throughout - don't let them lift to help move the weight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Leg+Curl+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chest Press Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A guided alternative to the bench press for building pressing strength without needing a spotter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjust the seat height first so the handles line up with mid-chest, not the shoulders or the collarbone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Chest+Press+Machine+form+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrist Wrench Roll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrist Wrench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A lever (often a bar or PVC pipe with a rope and weight attached) rotated by the wrists to roll the weight up, then lowered under control; builds forearm and wrist strength for grip-heavy lifts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start light - this is a small-muscle-group movement and forearms fatigue and strain easily if the load jumps too fast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/results?search_query=Wrist+Roller+forearm+training+technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional filename of a photo for this exercise, e.g. 'lat_pulldown.jpg'. Only works when importing via 'From spreadsheet + pictures (.zip)' - zip this spreadsheet together with the image files it names (using exactly these filenames; folder structure inside the zip doesn't matter) and import that zip instead of the plain spreadsheet. The photo attaches to the resulting exercise. Leave blank for rows that don't need one.</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1579,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1426,6 +1594,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1465,6 +1634,9 @@
       <c r="L1" s="1" t="s">
         <v>310</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -2794,6 +2966,321 @@
       </c>
       <c r="K39" s="5" t="s">
         <v>293</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -2830,7 +3317,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -2970,6 +3457,14 @@
         <v>313</v>
       </c>
       <c r="B20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>369</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/seed-data/strongman_exercise_database.xlsx
+++ b/seed-data/strongman_exercise_database.xlsx
@@ -908,7 +908,7 @@
     <t xml:space="preserve">About this sample exercise database</t>
   </si>
   <si>
-    <t xml:space="preserve">38 sample exercises covering warm-up, main barbell lifts, classic strongman odd-object events, loaded carries, pressing events, drag/pull events, accessory work, grip &amp; core, and conditioning. Intended as seed/test data for the exercise library, filtering, and the spreadsheet plan importer — not a verified or exhaustive reference for any specific federation's competition specs.</t>
+    <t xml:space="preserve">This is a real, fully-functional example library - 47 strongman-flavored exercises across warm-up, main barbell lifts, classic odd-object events, loaded carries, pressing/pulling events, accessory work, grip &amp; core, and conditioning. It ships as the app's default built-in library, and doubles as a filled-in example of every column below, so you can see exactly what a real row looks like before building your own. Nothing here is fixed - replace, extend, or delete any of it and import the result to make the library your own; it's not a verified or exhaustive reference for any specific federation's competition specs either way.</t>
   </si>
   <si>
     <t xml:space="preserve">Column</t>

--- a/seed-data/strongman_exercise_database.xlsx
+++ b/seed-data/strongman_exercise_database.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="372">
   <si>
     <t xml:space="preserve">Exercise ID</t>
   </si>
@@ -963,7 +963,7 @@
   </si>
   <si>
     <t xml:space="preserve">If you already have a list of exercises written down somewhere (a document, notes app, an old spreadsheet, or a coach's program), you can ask an AI assistant to fill in this template for you instead of doing it by hand. Attach this file to your AI assistant of choice and adapt this prompt:
-"I'm attaching a spreadsheet template for a workout-tracking app's exercise library. Fill in the 'Exercises' tab using the exercise list I describe below, following the 'Legend' tab's column definitions exactly - Difficulty must be exactly one of Beginner/Intermediate/Advanced. Leave the 'Embedding' column blank unless I specifically tell you a video should be embedded, and never invent a video link yourself. Don't guess or invent values for any column I haven't given you information for - leave those cells blank instead. Return the completed spreadsheet in the same column order as the template.
+"I'm attaching a spreadsheet template for a workout-tracking app's exercise library. Fill in the 'Exercises' tab using the exercise list I describe below, following the 'Legend' tab's column definitions exactly - Difficulty must be exactly one of Beginner/Intermediate/Advanced. Leave the 'Embedding' column blank unless I specifically tell you a video should be embedded, and never invent a video link yourself. Fill in 'Author' only if I tell you this list is from a specific coach/creator, with their name exactly as I give it to you. Don't guess or invent values for any column I haven't given you information for - leave those cells blank instead. Return the completed spreadsheet in the same column order as the template.
 [describe your exercises here, or paste your existing list]"</t>
   </si>
   <si>
@@ -1133,6 +1133,12 @@
   </si>
   <si>
     <t xml:space="preserve">Optional filename of a photo for this exercise, e.g. 'lat_pulldown.jpg'. Only works when importing via 'From spreadsheet + pictures (.zip)' - zip this spreadsheet together with the image files it names (using exactly these filenames; folder structure inside the zip doesn't matter) and import that zip instead of the plain spreadsheet. The photo attaches to the resulting exercise. Leave blank for rows that don't need one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional free-text creator name for this exercise (e.g. a coach's name). Every exercise sharing one Author value shows up as a single named, manageable group in the Exercise Library's own "Manage libraries &amp; blocks" screen - export, rename, or delete that whole imported set at once. Leave blank for an exercise you're not attributing to anyone in particular.</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1585,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1595,6 +1601,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1636,6 +1643,9 @@
       </c>
       <c r="M1" s="1" t="s">
         <v>368</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3317,7 +3327,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -3464,6 +3474,14 @@
       </c>
       <c r="B21" s="10" t="s">
         <v>369</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
